--- a/output/Coastal/TestEnvData.xlsx
+++ b/output/Coastal/TestEnvData.xlsx
@@ -604,213 +604,213 @@
         <v>MatchType</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>07/01/2025</v>
       </c>
       <c r="B2" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="C2" t="str">
+        <v>$30.00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>$30.00</v>
+      </c>
+      <c r="E2" t="str">
+        <v>RFMS</v>
+      </c>
+      <c r="F2" t="str">
+        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B3" t="str">
         <v>07/02/2025</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
+        <v>$1,639.05</v>
+      </c>
+      <c r="D3" t="str">
+        <v>$1,639.05</v>
+      </c>
+      <c r="E3" t="str">
+        <v>UHC</v>
+      </c>
+      <c r="F3" t="str">
+        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B4" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="C4" t="str">
+        <v>$2,581.65</v>
+      </c>
+      <c r="D4" t="str">
+        <v>$2,581.65</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Humana</v>
+      </c>
+      <c r="F4" t="str">
+        <v>HMP HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B5" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="C5" t="str">
+        <v>$4,400.00</v>
+      </c>
+      <c r="D5" t="str">
+        <v>$4,400.00</v>
+      </c>
+      <c r="E5" t="str">
+        <v>UHC</v>
+      </c>
+      <c r="F5" t="str">
+        <v>UNITEDHEALTHCARE HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B6" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="C6" t="str">
+        <v>$6,587.97</v>
+      </c>
+      <c r="D6" t="str">
+        <v>$6,587.97</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Humana</v>
+      </c>
+      <c r="F6" t="str">
+        <v>HMP HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B7" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="C7" t="str">
+        <v>$7,056.90</v>
+      </c>
+      <c r="D7" t="str">
+        <v>$7,056.90</v>
+      </c>
+      <c r="E7" t="str">
+        <v>UHC</v>
+      </c>
+      <c r="F7" t="str">
+        <v>UHC Community Pl HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B8" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="C8" t="str">
+        <v>$13,927.48</v>
+      </c>
+      <c r="D8" t="str">
+        <v>$13,927.48</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Humana</v>
+      </c>
+      <c r="F8" t="str">
+        <v>HMP HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B9" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="C9" t="str">
+        <v>$15,148.19</v>
+      </c>
+      <c r="D9" t="str">
+        <v>$15,148.19</v>
+      </c>
+      <c r="E9" t="str">
+        <v>MCR</v>
+      </c>
+      <c r="F9" t="str">
+        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B10" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="C10" t="str">
         <v>$15,848.71</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D10" t="str">
         <v>$15,848.71</v>
       </c>
-      <c r="E2" t="str" xml:space="preserve">
+      <c r="E10" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $4,217.54 (Wellmed CC | 7/1)
 2: $11,286.17 (Wellmed CC | 7/1)
 3: $345.00 (CC | 7/1)</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F10" t="str">
         <v>BANKCARD BTOT DEP CCD</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G10" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B3" t="str">
-        <v>07/02/2025</v>
-      </c>
-      <c r="C3" t="str">
-        <v>$15,148.19</v>
-      </c>
-      <c r="D3" t="str">
-        <v>$15,148.19</v>
-      </c>
-      <c r="E3" t="str">
-        <v>MCR</v>
-      </c>
-      <c r="F3" t="str">
-        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B4" t="str">
-        <v>07/03/2025</v>
-      </c>
-      <c r="C4" t="str">
-        <v>$6,587.97</v>
-      </c>
-      <c r="D4" t="str">
-        <v>$6,587.97</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Humana</v>
-      </c>
-      <c r="F4" t="str">
-        <v>HMP HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B5" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="C5" t="str">
-        <v>$2,581.65</v>
-      </c>
-      <c r="D5" t="str">
-        <v>$2,581.65</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Humana</v>
-      </c>
-      <c r="F5" t="str">
-        <v>HMP HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B6" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="C6" t="str">
-        <v>$13,927.48</v>
-      </c>
-      <c r="D6" t="str">
-        <v>$13,927.48</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Humana</v>
-      </c>
-      <c r="F6" t="str">
-        <v>HMP HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B7" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="C7" t="str">
-        <v>$30.00</v>
-      </c>
-      <c r="D7" t="str">
-        <v>$30.00</v>
-      </c>
-      <c r="E7" t="str">
-        <v>RFMS</v>
-      </c>
-      <c r="F7" t="str">
-        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B8" t="str">
-        <v>07/02/2025</v>
-      </c>
-      <c r="C8" t="str">
-        <v>$25,715.20</v>
-      </c>
-      <c r="D8" t="str">
-        <v>$25,715.20</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Sunshine</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Sunshine State H HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B9" t="str">
-        <v>07/02/2025</v>
-      </c>
-      <c r="C9" t="str">
-        <v>$7,056.90</v>
-      </c>
-      <c r="D9" t="str">
-        <v>$7,056.90</v>
-      </c>
-      <c r="E9" t="str">
-        <v>UHC</v>
-      </c>
-      <c r="F9" t="str">
-        <v>UHC Community Pl HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B10" t="str">
-        <v>07/02/2025</v>
-      </c>
-      <c r="C10" t="str">
-        <v>$92,666.42</v>
-      </c>
-      <c r="D10" t="str">
-        <v>$92,666.42</v>
-      </c>
-      <c r="E10" t="str">
-        <v>UHC</v>
-      </c>
-      <c r="F10" t="str">
-        <v>UHC Community Pl HCCLAIMPMT CCD</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="11">
@@ -821,16 +821,16 @@
         <v>07/02/2025</v>
       </c>
       <c r="C11" t="str">
-        <v>$39,269.09</v>
+        <v>$25,715.20</v>
       </c>
       <c r="D11" t="str">
-        <v>$39,269.09</v>
+        <v>$25,715.20</v>
       </c>
       <c r="E11" t="str">
-        <v>UHC</v>
+        <v>Sunshine</v>
       </c>
       <c r="F11" t="str">
-        <v>UHC Community Pl HCCLAIMPMT CCD</v>
+        <v>Sunshine State H HCCLAIMPMT CCD</v>
       </c>
       <c r="G11" t="str">
         <v>Exact</v>
@@ -844,16 +844,16 @@
         <v>07/02/2025</v>
       </c>
       <c r="C12" t="str">
-        <v>$1,639.05</v>
+        <v>$39,269.09</v>
       </c>
       <c r="D12" t="str">
-        <v>$1,639.05</v>
+        <v>$39,269.09</v>
       </c>
       <c r="E12" t="str">
         <v>UHC</v>
       </c>
       <c r="F12" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+        <v>UHC Community Pl HCCLAIMPMT CCD</v>
       </c>
       <c r="G12" t="str">
         <v>Exact</v>
@@ -864,19 +864,19 @@
         <v>07/01/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>07/03/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="C13" t="str">
-        <v>$4,400.00</v>
+        <v>$92,666.42</v>
       </c>
       <c r="D13" t="str">
-        <v>$4,400.00</v>
+        <v>$92,666.42</v>
       </c>
       <c r="E13" t="str">
         <v>UHC</v>
       </c>
       <c r="F13" t="str">
-        <v>UNITEDHEALTHCARE HCCLAIMPMT CCD</v>
+        <v>UHC Community Pl HCCLAIMPMT CCD</v>
       </c>
       <c r="G13" t="str">
         <v>Exact</v>
@@ -936,16 +936,16 @@
         <v>07/03/2025</v>
       </c>
       <c r="C16" t="str">
-        <v>$23,145.00</v>
+        <v>$5,280.00</v>
       </c>
       <c r="D16" t="str">
-        <v>$23,145.00</v>
+        <v>$5,280.00</v>
       </c>
       <c r="E16" t="str">
-        <v>RFMS</v>
+        <v>UHC</v>
       </c>
       <c r="F16" t="str">
-        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
+        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
       </c>
       <c r="G16" t="str">
         <v>Exact</v>
@@ -959,16 +959,16 @@
         <v>07/03/2025</v>
       </c>
       <c r="C17" t="str">
-        <v>$5,280.00</v>
+        <v>$23,145.00</v>
       </c>
       <c r="D17" t="str">
-        <v>$5,280.00</v>
+        <v>$23,145.00</v>
       </c>
       <c r="E17" t="str">
-        <v>UHC</v>
+        <v>RFMS</v>
       </c>
       <c r="F17" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
       </c>
       <c r="G17" t="str">
         <v>Exact</v>
@@ -982,16 +982,16 @@
         <v>07/07/2025</v>
       </c>
       <c r="C18" t="str">
-        <v>$2,700.27</v>
+        <v>$717.00</v>
       </c>
       <c r="D18" t="str">
-        <v>$2,700.27</v>
+        <v>$717.00</v>
       </c>
       <c r="E18" t="str">
-        <v>CC</v>
+        <v>Sunshine</v>
       </c>
       <c r="F18" t="str">
-        <v>BANKCARD BTOT DEP CCD</v>
+        <v>Sunshine State H HCCLAIMPMT CCD</v>
       </c>
       <c r="G18" t="str">
         <v>Exact</v>
@@ -1005,16 +1005,16 @@
         <v>07/07/2025</v>
       </c>
       <c r="C19" t="str">
-        <v>$717.00</v>
+        <v>$2,700.27</v>
       </c>
       <c r="D19" t="str">
-        <v>$717.00</v>
+        <v>$2,700.27</v>
       </c>
       <c r="E19" t="str">
-        <v>Sunshine</v>
+        <v>CC</v>
       </c>
       <c r="F19" t="str">
-        <v>Sunshine State H HCCLAIMPMT CCD</v>
+        <v>BANKCARD BTOT DEP CCD</v>
       </c>
       <c r="G19" t="str">
         <v>Exact</v>
@@ -1025,19 +1025,19 @@
         <v>07/07/2025</v>
       </c>
       <c r="B20" t="str">
-        <v>07/07/2025</v>
+        <v>07/09/2025</v>
       </c>
       <c r="C20" t="str">
-        <v>$900.00</v>
+        <v>$86.80</v>
       </c>
       <c r="D20" t="str">
-        <v>$900.00</v>
+        <v>$86.80</v>
       </c>
       <c r="E20" t="str">
-        <v>Careplus</v>
+        <v>CC</v>
       </c>
       <c r="F20" t="str">
-        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+        <v>BANKCARD BTOT DEP CCD</v>
       </c>
       <c r="G20" t="str">
         <v>Exact</v>
@@ -1048,19 +1048,19 @@
         <v>07/07/2025</v>
       </c>
       <c r="B21" t="str">
-        <v>07/09/2025</v>
+        <v>07/07/2025</v>
       </c>
       <c r="C21" t="str">
-        <v>$86.80</v>
+        <v>$900.00</v>
       </c>
       <c r="D21" t="str">
-        <v>$86.80</v>
+        <v>$900.00</v>
       </c>
       <c r="E21" t="str">
-        <v>CC</v>
+        <v>Careplus</v>
       </c>
       <c r="F21" t="str">
-        <v>BANKCARD BTOT DEP CCD</v>
+        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
       </c>
       <c r="G21" t="str">
         <v>Exact</v>
@@ -1097,90 +1097,90 @@
         <v>07/08/2025</v>
       </c>
       <c r="C23" t="str">
-        <v>$10,800.00</v>
+        <v>$81.50</v>
       </c>
       <c r="D23" t="str">
-        <v>$10,800.00</v>
+        <v>$81.50</v>
       </c>
       <c r="E23" t="str">
-        <v>Careplus</v>
+        <v>Deposit</v>
       </c>
       <c r="F23" t="str">
-        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+        <v>REMOTE DEPOSIT REF#</v>
       </c>
       <c r="G23" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="24" xml:space="preserve">
+    <row r="24">
       <c r="A24" t="str">
         <v>07/08/2025</v>
       </c>
       <c r="B24" t="str">
+        <v>07/08/2025</v>
+      </c>
+      <c r="C24" t="str">
+        <v>$1,051.00</v>
+      </c>
+      <c r="D24" t="str">
+        <v>$1,051.00</v>
+      </c>
+      <c r="E24" t="str">
+        <v>RFMS</v>
+      </c>
+      <c r="F24" t="str">
+        <v>NATL DATACARE CRT#A DEP RECORD #D</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>07/08/2025</v>
+      </c>
+      <c r="B25" t="str">
+        <v>07/08/2025</v>
+      </c>
+      <c r="C25" t="str">
+        <v>$10,800.00</v>
+      </c>
+      <c r="D25" t="str">
+        <v>$10,800.00</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Careplus</v>
+      </c>
+      <c r="F25" t="str">
+        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>07/08/2025</v>
+      </c>
+      <c r="B26" t="str">
         <v>07/10/2025</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C26" t="str">
         <v>$17,730.40</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D26" t="str">
         <v>$17,730.40</v>
       </c>
-      <c r="E24" t="str" xml:space="preserve">
+      <c r="E26" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $12,621.40 (CC | 7/8)
 2: $621.00 (CC | 7/8)
 3: $4,488.00 (CC | 7/8)</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F26" t="str">
         <v>BANKCARD BTOT DEP CCD</v>
       </c>
-      <c r="G24" t="str">
+      <c r="G26" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>07/08/2025</v>
-      </c>
-      <c r="B25" t="str">
-        <v>07/08/2025</v>
-      </c>
-      <c r="C25" t="str">
-        <v>$1,051.00</v>
-      </c>
-      <c r="D25" t="str">
-        <v>$1,051.00</v>
-      </c>
-      <c r="E25" t="str">
-        <v>RFMS</v>
-      </c>
-      <c r="F25" t="str">
-        <v>NATL DATACARE CRT#A DEP RECORD #D</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>07/08/2025</v>
-      </c>
-      <c r="B26" t="str">
-        <v>07/08/2025</v>
-      </c>
-      <c r="C26" t="str">
-        <v>$19,833.45</v>
-      </c>
-      <c r="D26" t="str">
-        <v>$19,833.45</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Deposit</v>
-      </c>
-      <c r="F26" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="27">
@@ -1191,10 +1191,10 @@
         <v>07/08/2025</v>
       </c>
       <c r="C27" t="str">
-        <v>$81.50</v>
+        <v>$19,833.45</v>
       </c>
       <c r="D27" t="str">
-        <v>$81.50</v>
+        <v>$19,833.45</v>
       </c>
       <c r="E27" t="str">
         <v>Deposit</v>
@@ -1326,19 +1326,19 @@
         <v>07/11/2025</v>
       </c>
       <c r="B33" t="str">
-        <v>07/14/2025</v>
+        <v>07/15/2025</v>
       </c>
       <c r="C33" t="str">
-        <v>$9,677.92</v>
+        <v>$4,244.43</v>
       </c>
       <c r="D33" t="str">
-        <v>$9,677.92</v>
+        <v>$4,244.43</v>
       </c>
       <c r="E33" t="str">
-        <v>Sunshine</v>
+        <v>UHC</v>
       </c>
       <c r="F33" t="str">
-        <v>Sunshine State H HCCLAIMPMT CCD</v>
+        <v>UHC Community Pl HCCLAIMPMT CCD</v>
       </c>
       <c r="G33" t="str">
         <v>Exact</v>
@@ -1349,19 +1349,19 @@
         <v>07/11/2025</v>
       </c>
       <c r="B34" t="str">
-        <v>07/15/2025</v>
+        <v>07/14/2025</v>
       </c>
       <c r="C34" t="str">
-        <v>$4,244.43</v>
+        <v>$9,677.92</v>
       </c>
       <c r="D34" t="str">
-        <v>$4,244.43</v>
+        <v>$9,677.92</v>
       </c>
       <c r="E34" t="str">
-        <v>UHC</v>
+        <v>Sunshine</v>
       </c>
       <c r="F34" t="str">
-        <v>UHC Community Pl HCCLAIMPMT CCD</v>
+        <v>Sunshine State H HCCLAIMPMT CCD</v>
       </c>
       <c r="G34" t="str">
         <v>Exact</v>
@@ -1464,19 +1464,19 @@
         <v>07/15/2025</v>
       </c>
       <c r="B39" t="str">
-        <v>07/16/2025</v>
+        <v>07/15/2025</v>
       </c>
       <c r="C39" t="str">
-        <v>$9,001.00</v>
+        <v>$5,136.16</v>
       </c>
       <c r="D39" t="str">
-        <v>$9,001.00</v>
+        <v>$5,136.16</v>
       </c>
       <c r="E39" t="str">
-        <v>MCR</v>
+        <v>Deposit</v>
       </c>
       <c r="F39" t="str">
-        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
+        <v>REMOTE DEPOSIT REF#</v>
       </c>
       <c r="G39" t="str">
         <v>Exact</v>
@@ -1487,19 +1487,19 @@
         <v>07/15/2025</v>
       </c>
       <c r="B40" t="str">
-        <v>07/15/2025</v>
+        <v>07/16/2025</v>
       </c>
       <c r="C40" t="str">
-        <v>$5,136.16</v>
+        <v>$9,001.00</v>
       </c>
       <c r="D40" t="str">
-        <v>$5,136.16</v>
+        <v>$9,001.00</v>
       </c>
       <c r="E40" t="str">
-        <v>Deposit</v>
+        <v>MCR</v>
       </c>
       <c r="F40" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
+        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
       </c>
       <c r="G40" t="str">
         <v>Exact</v>
@@ -1510,19 +1510,19 @@
         <v>07/16/2025</v>
       </c>
       <c r="B41" t="str">
-        <v>07/17/2025</v>
+        <v>07/18/2025</v>
       </c>
       <c r="C41" t="str">
-        <v>$31,207.22</v>
+        <v>$157.99</v>
       </c>
       <c r="D41" t="str">
-        <v>$31,207.22</v>
+        <v>$157.99</v>
       </c>
       <c r="E41" t="str">
-        <v>MCD</v>
+        <v>UHC</v>
       </c>
       <c r="F41" t="str">
-        <v>ACH MEDICAID HCCLAIMPMT CCD</v>
+        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
       </c>
       <c r="G41" t="str">
         <v>Exact</v>
@@ -1556,72 +1556,72 @@
         <v>07/16/2025</v>
       </c>
       <c r="B43" t="str">
-        <v>07/18/2025</v>
+        <v>07/17/2025</v>
       </c>
       <c r="C43" t="str">
-        <v>$157.99</v>
+        <v>$31,207.22</v>
       </c>
       <c r="D43" t="str">
-        <v>$157.99</v>
+        <v>$31,207.22</v>
       </c>
       <c r="E43" t="str">
-        <v>UHC</v>
+        <v>MCD</v>
       </c>
       <c r="F43" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+        <v>ACH MEDICAID HCCLAIMPMT CCD</v>
       </c>
       <c r="G43" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="44" xml:space="preserve">
-      <c r="A44" t="str" xml:space="preserve">
+    <row r="44">
+      <c r="A44" t="str">
+        <v>07/17/2025</v>
+      </c>
+      <c r="B44" t="str">
+        <v>07/17/2025</v>
+      </c>
+      <c r="C44" t="str">
+        <v>$2,013.00</v>
+      </c>
+      <c r="D44" t="str">
+        <v>$2,013.00</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Deposit</v>
+      </c>
+      <c r="F44" t="str">
+        <v>REMOTE DEPOSIT REF#</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str" xml:space="preserve">
         <v xml:space="preserve">07/17/2025
 -
 07/18/2025</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B45" t="str">
         <v>07/21/2025</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C45" t="str">
         <v>$48,320.58</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D45" t="str">
         <v>$48,320.58</v>
       </c>
-      <c r="E44" t="str" xml:space="preserve">
+      <c r="E45" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $14,147.18 (Hospice | 7/17)
 2: $7,894.75 (Hospice | 7/18)
 3: $26,278.65 (CC | 7/18)</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F45" t="str">
         <v>BANKCARD BTOT DEP CCD</v>
       </c>
-      <c r="G44" t="str">
+      <c r="G45" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>07/17/2025</v>
-      </c>
-      <c r="B45" t="str">
-        <v>07/17/2025</v>
-      </c>
-      <c r="C45" t="str">
-        <v>$2,013.00</v>
-      </c>
-      <c r="D45" t="str">
-        <v>$2,013.00</v>
-      </c>
-      <c r="E45" t="str">
-        <v>Deposit</v>
-      </c>
-      <c r="F45" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="46">
@@ -1632,16 +1632,16 @@
         <v>07/18/2025</v>
       </c>
       <c r="C46" t="str">
-        <v>$9,838.45</v>
+        <v>$9,629.42</v>
       </c>
       <c r="D46" t="str">
-        <v>$9,838.45</v>
+        <v>$9,629.42</v>
       </c>
       <c r="E46" t="str">
-        <v>Optum</v>
+        <v>Deposit</v>
       </c>
       <c r="F46" t="str">
-        <v>Optum VA CCN Reg HCCLAIMPMT CCD</v>
+        <v>REMOTE DEPOSIT REF#</v>
       </c>
       <c r="G46" t="str">
         <v>Exact</v>
@@ -1655,16 +1655,16 @@
         <v>07/18/2025</v>
       </c>
       <c r="C47" t="str">
-        <v>$9,629.42</v>
+        <v>$9,838.45</v>
       </c>
       <c r="D47" t="str">
-        <v>$9,629.42</v>
+        <v>$9,838.45</v>
       </c>
       <c r="E47" t="str">
-        <v>Deposit</v>
+        <v>Optum</v>
       </c>
       <c r="F47" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
+        <v>Optum VA CCN Reg HCCLAIMPMT CCD</v>
       </c>
       <c r="G47" t="str">
         <v>Exact</v>
@@ -1698,19 +1698,19 @@
         <v>07/19/2025</v>
       </c>
       <c r="B49" t="str">
-        <v>07/21/2025</v>
+        <v>07/23/2025</v>
       </c>
       <c r="C49" t="str">
-        <v>$40.52</v>
+        <v>$26.85</v>
       </c>
       <c r="D49" t="str">
-        <v>$40.52</v>
+        <v>$26.85</v>
       </c>
       <c r="E49" t="str">
-        <v>Careplus</v>
+        <v>UHC</v>
       </c>
       <c r="F49" t="str">
-        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
       </c>
       <c r="G49" t="str">
         <v>Exact</v>
@@ -1721,19 +1721,19 @@
         <v>07/19/2025</v>
       </c>
       <c r="B50" t="str">
-        <v>07/23/2025</v>
+        <v>07/21/2025</v>
       </c>
       <c r="C50" t="str">
-        <v>$26.85</v>
+        <v>$40.52</v>
       </c>
       <c r="D50" t="str">
-        <v>$26.85</v>
+        <v>$40.52</v>
       </c>
       <c r="E50" t="str">
-        <v>UHC</v>
+        <v>Careplus</v>
       </c>
       <c r="F50" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
       </c>
       <c r="G50" t="str">
         <v>Exact</v>
@@ -1790,19 +1790,19 @@
         <v>07/22/2025</v>
       </c>
       <c r="B53" t="str">
-        <v>07/22/2025</v>
+        <v>07/25/2025</v>
       </c>
       <c r="C53" t="str">
-        <v>$7,751.50</v>
+        <v>$6.83</v>
       </c>
       <c r="D53" t="str">
-        <v>$7,751.50</v>
+        <v>$6.83</v>
       </c>
       <c r="E53" t="str">
-        <v>AARP</v>
+        <v>Humana</v>
       </c>
       <c r="F53" t="str">
-        <v>AARP Supplementa HCCLAIMPMT CCD</v>
+        <v>HMP HCCLAIMPMT CCD</v>
       </c>
       <c r="G53" t="str">
         <v>Exact</v>
@@ -1813,19 +1813,19 @@
         <v>07/22/2025</v>
       </c>
       <c r="B54" t="str">
-        <v>07/23/2025</v>
+        <v>07/22/2025</v>
       </c>
       <c r="C54" t="str">
-        <v>$209,876.71</v>
+        <v>$181.00</v>
       </c>
       <c r="D54" t="str">
-        <v>$209,876.71</v>
+        <v>$181.00</v>
       </c>
       <c r="E54" t="str">
-        <v>MCR</v>
+        <v>RFMS</v>
       </c>
       <c r="F54" t="str">
-        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
+        <v>NATL DATACARE CRT#AC WDL RECORD #W</v>
       </c>
       <c r="G54" t="str">
         <v>Exact</v>
@@ -1836,19 +1836,19 @@
         <v>07/22/2025</v>
       </c>
       <c r="B55" t="str">
-        <v>07/25/2025</v>
+        <v>07/22/2025</v>
       </c>
       <c r="C55" t="str">
-        <v>$6.83</v>
+        <v>$2,095.00</v>
       </c>
       <c r="D55" t="str">
-        <v>$6.83</v>
+        <v>$2,095.00</v>
       </c>
       <c r="E55" t="str">
-        <v>Humana</v>
+        <v>Deposit</v>
       </c>
       <c r="F55" t="str">
-        <v>HMP HCCLAIMPMT CCD</v>
+        <v>REMOTE DEPOSIT REF#</v>
       </c>
       <c r="G55" t="str">
         <v>Exact</v>
@@ -1862,16 +1862,16 @@
         <v>07/22/2025</v>
       </c>
       <c r="C56" t="str">
-        <v>$181.00</v>
+        <v>$7,751.50</v>
       </c>
       <c r="D56" t="str">
-        <v>$181.00</v>
+        <v>$7,751.50</v>
       </c>
       <c r="E56" t="str">
-        <v>RFMS</v>
+        <v>AARP</v>
       </c>
       <c r="F56" t="str">
-        <v>NATL DATACARE CRT#AC WDL RECORD #W</v>
+        <v>AARP Supplementa HCCLAIMPMT CCD</v>
       </c>
       <c r="G56" t="str">
         <v>Exact</v>
@@ -1882,19 +1882,19 @@
         <v>07/22/2025</v>
       </c>
       <c r="B57" t="str">
-        <v>07/22/2025</v>
+        <v>07/23/2025</v>
       </c>
       <c r="C57" t="str">
-        <v>$2,095.00</v>
+        <v>$209,876.71</v>
       </c>
       <c r="D57" t="str">
-        <v>$2,095.00</v>
+        <v>$209,876.71</v>
       </c>
       <c r="E57" t="str">
-        <v>Deposit</v>
+        <v>MCR</v>
       </c>
       <c r="F57" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
+        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
       </c>
       <c r="G57" t="str">
         <v>Exact</v>
@@ -1954,16 +1954,16 @@
         <v>07/28/2025</v>
       </c>
       <c r="C60" t="str">
-        <v>$614.00</v>
+        <v>$6.71</v>
       </c>
       <c r="D60" t="str">
-        <v>$614.00</v>
+        <v>$6.71</v>
       </c>
       <c r="E60" t="str">
-        <v>CC</v>
+        <v>UHC</v>
       </c>
       <c r="F60" t="str">
-        <v>BANKCARD BTOT DEP CCD</v>
+        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
       </c>
       <c r="G60" t="str">
         <v>Exact</v>
@@ -1974,19 +1974,19 @@
         <v>07/24/2025</v>
       </c>
       <c r="B61" t="str">
-        <v>07/24/2025</v>
+        <v>07/28/2025</v>
       </c>
       <c r="C61" t="str">
-        <v>$1,641.00</v>
+        <v>$614.00</v>
       </c>
       <c r="D61" t="str">
-        <v>$1,641.00</v>
+        <v>$614.00</v>
       </c>
       <c r="E61" t="str">
-        <v>Deposit</v>
+        <v>CC</v>
       </c>
       <c r="F61" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
+        <v>BANKCARD BTOT DEP CCD</v>
       </c>
       <c r="G61" t="str">
         <v>Exact</v>
@@ -2020,19 +2020,19 @@
         <v>07/24/2025</v>
       </c>
       <c r="B63" t="str">
-        <v>07/28/2025</v>
+        <v>07/24/2025</v>
       </c>
       <c r="C63" t="str">
-        <v>$6.71</v>
+        <v>$1,641.00</v>
       </c>
       <c r="D63" t="str">
-        <v>$6.71</v>
+        <v>$1,641.00</v>
       </c>
       <c r="E63" t="str">
-        <v>UHC</v>
+        <v>Deposit</v>
       </c>
       <c r="F63" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+        <v>REMOTE DEPOSIT REF#</v>
       </c>
       <c r="G63" t="str">
         <v>Exact</v>
@@ -2046,16 +2046,16 @@
         <v>07/29/2025</v>
       </c>
       <c r="C64" t="str">
-        <v>$174,292.51</v>
+        <v>$10,013.00</v>
       </c>
       <c r="D64" t="str">
-        <v>$174,292.51</v>
+        <v>$10,013.00</v>
       </c>
       <c r="E64" t="str">
-        <v>FLCC</v>
+        <v>UHC</v>
       </c>
       <c r="F64" t="str">
-        <v>FLORIDA COMMUNI HCCLAIMPMT CCD</v>
+        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
       </c>
       <c r="G64" t="str">
         <v>Exact</v>
@@ -2092,16 +2092,16 @@
         <v>07/29/2025</v>
       </c>
       <c r="C66" t="str">
-        <v>$10,013.00</v>
+        <v>$174,292.51</v>
       </c>
       <c r="D66" t="str">
-        <v>$10,013.00</v>
+        <v>$174,292.51</v>
       </c>
       <c r="E66" t="str">
-        <v>UHC</v>
+        <v>FLCC</v>
       </c>
       <c r="F66" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT CCD</v>
+        <v>FLORIDA COMMUNI HCCLAIMPMT CCD</v>
       </c>
       <c r="G66" t="str">
         <v>Exact</v>
@@ -2158,19 +2158,19 @@
         <v>07/29/2025</v>
       </c>
       <c r="B69" t="str">
-        <v>07/30/2025</v>
+        <v>07/29/2025</v>
       </c>
       <c r="C69" t="str">
-        <v>$9,954.30</v>
+        <v>$573.00</v>
       </c>
       <c r="D69" t="str">
-        <v>$9,954.30</v>
+        <v>$573.00</v>
       </c>
       <c r="E69" t="str">
-        <v>MCR</v>
+        <v>Deposit</v>
       </c>
       <c r="F69" t="str">
-        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
+        <v>REMOTE DEPOSIT REF#</v>
       </c>
       <c r="G69" t="str">
         <v>Exact</v>
@@ -2181,19 +2181,19 @@
         <v>07/29/2025</v>
       </c>
       <c r="B70" t="str">
-        <v>07/29/2025</v>
+        <v>07/30/2025</v>
       </c>
       <c r="C70" t="str">
-        <v>$573.00</v>
+        <v>$9,954.30</v>
       </c>
       <c r="D70" t="str">
-        <v>$573.00</v>
+        <v>$9,954.30</v>
       </c>
       <c r="E70" t="str">
-        <v>Deposit</v>
+        <v>MCR</v>
       </c>
       <c r="F70" t="str">
-        <v>REMOTE DEPOSIT REF#</v>
+        <v>FIRST COAST SERV HCCLAIMPMT CCD</v>
       </c>
       <c r="G70" t="str">
         <v>Exact</v>
@@ -2252,7 +2252,7 @@
         <v>07/14/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$-359.69</v>
+        <v>-$359.69</v>
       </c>
       <c r="C2" t="str">
         <v>Sunshine Really$0.00</v>
@@ -2564,7 +2564,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E2" t="str">
-        <v>COASTAL CENTER OPERATIONS LLC MONOGRAM CHECKING 1503764063</v>
+        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="3">
@@ -2581,7 +2581,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E3" t="str">
-        <v>COASTAL CENTER OPERATIONS LLC MONOGRAM CHECKING 1503764063</v>
+        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="4">
@@ -2598,7 +2598,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E4" t="str">
-        <v>COASTAL CENTER OPERATIONS LLC MONOGRAM CHECKING 1503764063</v>
+        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="5">
@@ -2615,7 +2615,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E5" t="str">
-        <v>COASTAL CENTER OPERATIONS LLC MONOGRAM CHECKING 1503764063</v>
+        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="6">
@@ -2632,7 +2632,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E6" t="str">
-        <v>COASTAL CENTER OPERATIONS LLC MONOGRAM CHECKING 1503764063</v>
+        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="7">
@@ -2649,7 +2649,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E7" t="str">
-        <v>COASTAL CENTER OPERATIONS LLC MONOGRAM CHECKING 1503764063</v>
+        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="8">

--- a/output/Coastal/TestEnvData.xlsx
+++ b/output/Coastal/TestEnvData.xlsx
@@ -802,9 +802,9 @@
         <v>$15,848.71</v>
       </c>
       <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $4,217.54 (Wellmed CC | 7/1)
-2: $11,286.17 (Wellmed CC | 7/1)
-3: $345.00 (CC | 7/1)</v>
+        <v xml:space="preserve">1: $345.00 (CC | 7/1)
+2: $4,217.54 (Wellmed CC | 7/1)
+3: $11,286.17 (Wellmed CC | 7/1)</v>
       </c>
       <c r="F10" t="str">
         <v>BANKCARD BTOT DEP CCD</v>
@@ -1060,7 +1060,7 @@
         <v>Careplus</v>
       </c>
       <c r="F21" t="str">
-        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT COASTAL CENTER OPERATI</v>
       </c>
       <c r="G21" t="str">
         <v>Exact</v>
@@ -1152,7 +1152,7 @@
         <v>Careplus</v>
       </c>
       <c r="F25" t="str">
-        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT COASTAL CENTER OPERATI</v>
       </c>
       <c r="G25" t="str">
         <v>Exact</v>
@@ -1172,9 +1172,9 @@
         <v>$17,730.40</v>
       </c>
       <c r="E26" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $12,621.40 (CC | 7/8)
-2: $621.00 (CC | 7/8)
-3: $4,488.00 (CC | 7/8)</v>
+        <v xml:space="preserve">1: $621.00 (CC | 7/8)
+2: $4,488.00 (CC | 7/8)
+3: $12,621.40 (CC | 7/8)</v>
       </c>
       <c r="F26" t="str">
         <v>BANKCARD BTOT DEP CCD</v>
@@ -1733,7 +1733,7 @@
         <v>Careplus</v>
       </c>
       <c r="F50" t="str">
-        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT</v>
+        <v>ACH DEPOSIT HUMANA INC US LE HCCLAIMPMT COASTAL CENTER OPERATI</v>
       </c>
       <c r="G50" t="str">
         <v>Exact</v>
@@ -2392,7 +2392,7 @@
         <v>$7,181.53</v>
       </c>
       <c r="C4" t="str">
-        <v>ACH DEPOSIT ILUMED LLC HCCLAIMPMT</v>
+        <v>ACH DEPOSIT ILUMED LLC HCCLAIMPMT COASTAL CENTER OPERATI</v>
       </c>
       <c r="D4" t="str">
         <v>Unmatched</v>
@@ -2561,7 +2561,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E2" t="str">
-        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
+        <v>MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="3">
@@ -2578,7 +2578,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E3" t="str">
-        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
+        <v>MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="4">
@@ -2595,7 +2595,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E4" t="str">
-        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
+        <v>MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="5">
@@ -2612,7 +2612,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E5" t="str">
-        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
+        <v>MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="6">
@@ -2629,7 +2629,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E6" t="str">
-        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
+        <v>MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="7">
@@ -2646,7 +2646,7 @@
         <v>ACH DEPOSIT NDC SWEEP FAC B</v>
       </c>
       <c r="E7" t="str">
-        <v>Coastal Center Operations LLC MONOGRAM CHECKING 1503764063</v>
+        <v>MONOGRAM CHECKING 1503764063</v>
       </c>
     </row>
     <row r="8">
